--- a/public/routers/A0_Sistema_FV/A61_Conectado_a_red/FV01_Rendimiento_de_un_sistema_FV_conectado_a_red.xlsx
+++ b/public/routers/A0_Sistema_FV/A61_Conectado_a_red/FV01_Rendimiento_de_un_sistema_FV_conectado_a_red.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Casas en Guadalmar</t>
+          <t>Vivienda unifamiliar</t>
         </is>
       </c>
     </row>
@@ -517,11 +517,7 @@
           <t>nombre</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Instalaciones S..</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -535,11 +531,7 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>A12345678</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -607,11 +599,7 @@
           <t>nombre</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Ayto. Villanueva</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
